--- a/ai-service/matching_results.xlsx
+++ b/ai-service/matching_results.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Docker, SQL, Java</t>
+          <t>Java, SQL, Docker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALERT: Skill match 33.33% is below 85% requirement. Upskilling recommended in: Docker, Java</t>
+          <t>ALERT: Skill match 33.33% is below 85% requirement. Upskilling recommended in: Java, Docker</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Docker, Java</t>
+          <t>Java, Docker</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TensorFlow, Python, SQL</t>
+          <t>SQL, TensorFlow, Python</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Python, Kubernetes, SQL</t>
+          <t>SQL, Kubernetes, Python</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/ai-service/matching_results.xlsx
+++ b/ai-service/matching_results.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Java, SQL, Docker</t>
+          <t>Docker, SQL, Java</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ALERT: Skill match 33.33% is below 85% requirement. Upskilling recommended in: Java, Docker</t>
+          <t>ALERT: Skill match 33.33% is below 85% requirement. Upskilling recommended in: Docker, Java</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Java, Docker</t>
+          <t>Docker, Java</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SQL, TensorFlow, Python</t>
+          <t>Python, SQL, TensorFlow</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -629,17 +629,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ALERT: Skill match 60.0% is below 85% requirement. Upskilling recommended in: AWS SageMaker, TensorFlow</t>
+          <t>ALERT: Skill match 60.0% is below 85% requirement. Upskilling recommended in: TensorFlow, AWS SageMaker</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SQL, Kubernetes, Python</t>
+          <t>Python, SQL, Kubernetes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AWS SageMaker, TensorFlow</t>
+          <t>TensorFlow, AWS SageMaker</t>
         </is>
       </c>
     </row>
